--- a/consent_forms/038_video_commentary_publication_consent_form--consent_forms.xlsx
+++ b/consent_forms/038_video_commentary_publication_consent_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -528,10 +528,14 @@
           <t>Video Commentary Publication Consent</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please provide your consent for video commentary publication.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -551,7 +555,11 @@
           <t>Participant Name</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please enter your name.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -574,7 +582,11 @@
           <t>Participant Email</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please enter your email.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -594,10 +606,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Participant Phone</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Participant Phone Number</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please enter your phone number.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -620,7 +636,11 @@
           <t>Participant Address</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please enter your address.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -640,10 +660,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Participant Country</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Participant Country of Residence</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please select your country of residence.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>yes</t>
@@ -653,20 +677,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>participant_country_options</t>
+          <t>participant_video_commentary</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Participant Country</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Participant Video Commentary</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please enter your video commentary.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -676,20 +704,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>participant_video_commentary</t>
+          <t>participant_video_commentary_options</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Participant Video Commentary</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Participant Video Commentary Options</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Select one option.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -704,38 +736,46 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>participant_video_commentary_options</t>
+          <t>participant_agreement</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Participant Video Commentary Options</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Participant Agreement</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Select one option.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>participant_video_commentary_select_options</t>
+          <t>participant_agreement_options</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Participant Video Commentary</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Participant Agreement Options</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Select multiple options.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -750,15 +790,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>participant_video_commentary_select_option</t>
+          <t>participant_agreement_select_option</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Participant Video Commentary Select Option</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Participant Agreement Select Option</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Select one option.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -773,315 +817,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>participant_video_commentary_select_option</t>
+          <t>participant_agreement_select_option_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Participant Video Commentary Select Option</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Participant Agreement Select Option 2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Select one option.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>participant_agreement</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Participant Agreement</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>participant_agreement_options</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Participant Agreement</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>participant_agreement_select_options</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Participant Agreement</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>participant_agreement_select_option</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Participant Agreement Select Option</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>participant_agreement_select_options</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Participant Agreement Select Options</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>participant_agreement_options</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Participant Agreement Options</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>participant_agreement_options</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Participant Agreement Options</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>participant_agreement_select_option</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Participant Agreement Select Option</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>participant_agreement_select_option</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Participant Agreement Select Option</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>participant_agreement_select_option</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Participant Agreement Select Option</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>participant_agreement_select_option</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Participant Agreement Select Option</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>participant_agreement_select_option_2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Participant Agreement Select Option 2</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>participant_agreement_select_option_2</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Participant Agreement Select Option 2</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +847,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="47" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,7 +875,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>participant_country_choices</t>
+          <t>video_commentary_publication_consent_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +892,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>participant_country_choices</t>
+          <t>video_commentary_publication_consent_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,136 +909,136 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>participant_country_options_choices</t>
+          <t>participant_country_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>united_states</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>United States</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>participant_country_options_choices</t>
+          <t>participant_country_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>canada</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>participant_video_commentary_options_choices</t>
+          <t>participant_country_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>mexico</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Mexico</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>participant_video_commentary_options_choices</t>
+          <t>participant_country_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>participant_video_commentary_select_option_choices</t>
+          <t>participant_video_commentary_options_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes,_with_photos</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes, with photos</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>participant_video_commentary_select_option_choices</t>
+          <t>participant_video_commentary_options_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>no,_with_no_photos</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No, with no photos</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>participant_video_commentary_select_option_choices</t>
+          <t>participant_video_commentary_options_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes,_with_limited_photos</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes, with limited photos</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>participant_video_commentary_select_option_choices</t>
+          <t>participant_agreement_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1301,29 +1050,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>participant_agreement_choices</t>
+          <t>participant_agreement_options_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1335,401 +1084,78 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>participant_agreement_options_choices</t>
+          <t>participant_agreement_select_option_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>participant_agreement_select_options_choices</t>
+          <t>participant_agreement_select_option_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>participant_agreement_select_options_choices</t>
+          <t>participant_agreement_select_option_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>participant_agreement_select_option_choices</t>
+          <t>participant_agreement_select_option_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>participant_agreement_select_option_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>participant_agreement_select_options_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>participant_agreement_select_options_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>participant_agreement_options_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>participant_agreement_options_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>participant_agreement_options_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>participant_agreement_options_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>participant_agreement_select_option_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>participant_agreement_select_option_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>participant_agreement_select_option_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>participant_agreement_select_option_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>participant_agreement_select_option_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>participant_agreement_select_option_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>participant_agreement_select_option_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>participant_agreement_select_option_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>participant_agreement_select_option_2_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>participant_agreement_select_option_2_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>participant_agreement_select_option_2_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>participant_agreement_select_option_2_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
         <is>
           <t>No</t>
         </is>
